--- a/settings/data/DanmakuCreator.xlsx
+++ b/settings/data/DanmakuCreator.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="11630"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="d4c" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="117">
   <si>
     <t>string</t>
   </si>
@@ -371,6 +371,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">弹幕颜色
 </t>
     </r>
@@ -387,6 +394,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">发弹分段规则
 </t>
     </r>
@@ -756,6 +770,9 @@
   </si>
   <si>
     <t>0|360|20|160</t>
+  </si>
+  <si>
+    <t>240|0|0</t>
   </si>
   <si>
     <t>dcrt_keine_ns2_2</t>
@@ -966,7 +983,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="9"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -980,7 +997,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color theme="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2779,7 +2796,7 @@
         <v>73</v>
       </c>
       <c r="U11" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="Z11" t="s">
         <v>89</v>
@@ -2797,10 +2814,10 @@
     </row>
     <row r="12" s="1" customFormat="1" spans="1:29">
       <c r="A12" s="15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C12" s="1" t="str">
         <f>C11</f>
@@ -2884,10 +2901,10 @@
     </row>
     <row r="13" spans="1:29">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C13" t="str">
         <f>[4]danma!$A$9</f>
@@ -2897,7 +2914,7 @@
         <v>66</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -2942,19 +2959,19 @@
     </row>
     <row r="14" spans="1:29">
       <c r="A14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D14" t="s">
         <v>104</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -2994,7 +3011,7 @@
         <v>73</v>
       </c>
       <c r="U14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/settings/data/DanmakuCreator.xlsx
+++ b/settings/data/DanmakuCreator.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10709\Desktop\thloo\settings\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D566CF-C7FB-434A-8402-CFF13CD5659C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView xWindow="3705" yWindow="4320" windowWidth="32190" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="d4c" sheetId="1" r:id="rId1"/>
@@ -28,6 +34,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -730,9 +739,6 @@
     <t>dcrt_keine_sc1_2</t>
   </si>
   <si>
-    <t>慧音一符中的发弹点，发射自机狙激光</t>
-  </si>
-  <si>
     <t>500|0</t>
   </si>
   <si>
@@ -803,19 +809,17 @@
   </si>
   <si>
     <t>15|0|0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -835,150 +839,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1002,8 +862,22 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1012,222 +886,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.0499893185216834"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799890133365886"/>
+        <fgColor theme="5" tint="0.79985961485641044"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799890133365886"/>
+        <fgColor theme="8" tint="0.79985961485641044"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799890133365886"/>
+        <fgColor theme="7" tint="0.79985961485641044"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799890133365886"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.79985961485641044"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1250,255 +938,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1547,72 +993,31 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="danma"/>
@@ -1651,7 +1056,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="keine_routine"/>
@@ -1690,7 +1095,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Enemy"/>
@@ -1698,6 +1103,9 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="16">
+          <cell r="A16" t="str">
+            <v>enm_keine_ns1_1</v>
+          </cell>
           <cell r="G16">
             <v>30</v>
           </cell>
@@ -1724,7 +1132,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="danma"/>
@@ -1986,46 +1394,46 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="18.4454545454545" customWidth="1"/>
-    <col min="2" max="2" width="71.1090909090909" customWidth="1"/>
-    <col min="3" max="3" width="18.5545454545455" customWidth="1"/>
+    <col min="1" max="1" width="18.5" customWidth="1"/>
+    <col min="2" max="2" width="71.125" customWidth="1"/>
+    <col min="3" max="3" width="18.5" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="20.4454545454545" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.4454545454545" customWidth="1"/>
-    <col min="7" max="7" width="28.8909090909091" customWidth="1"/>
-    <col min="8" max="8" width="29.2181818181818" customWidth="1"/>
-    <col min="9" max="9" width="22.8909090909091" customWidth="1"/>
-    <col min="10" max="10" width="20.4454545454545" customWidth="1"/>
-    <col min="11" max="11" width="17.3363636363636" customWidth="1"/>
-    <col min="12" max="12" width="18.4454545454545" customWidth="1"/>
-    <col min="13" max="13" width="29.1090909090909" customWidth="1"/>
-    <col min="14" max="15" width="26.8909090909091" customWidth="1"/>
-    <col min="16" max="16" width="20.4454545454545" customWidth="1"/>
-    <col min="17" max="17" width="24.4454545454545" customWidth="1"/>
-    <col min="18" max="18" width="27.4454545454545" customWidth="1"/>
-    <col min="19" max="19" width="16.2181818181818" customWidth="1"/>
-    <col min="20" max="20" width="20.7818181818182" customWidth="1"/>
-    <col min="21" max="21" width="15.2181818181818" customWidth="1"/>
-    <col min="22" max="22" width="20.8909090909091" customWidth="1"/>
-    <col min="23" max="23" width="19.6636363636364" customWidth="1"/>
-    <col min="24" max="24" width="21.8909090909091" customWidth="1"/>
-    <col min="25" max="25" width="26.3363636363636" customWidth="1"/>
-    <col min="26" max="26" width="20.8909090909091" customWidth="1"/>
-    <col min="27" max="27" width="27.1090909090909" customWidth="1"/>
-    <col min="28" max="28" width="21.8909090909091" customWidth="1"/>
-    <col min="29" max="29" width="26.3363636363636" customWidth="1"/>
+    <col min="5" max="5" width="20.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.5" customWidth="1"/>
+    <col min="7" max="7" width="28.875" customWidth="1"/>
+    <col min="8" max="8" width="29.25" customWidth="1"/>
+    <col min="9" max="9" width="22.875" customWidth="1"/>
+    <col min="10" max="10" width="20.5" customWidth="1"/>
+    <col min="11" max="11" width="17.375" customWidth="1"/>
+    <col min="12" max="12" width="18.5" customWidth="1"/>
+    <col min="13" max="13" width="29.125" customWidth="1"/>
+    <col min="14" max="15" width="26.875" customWidth="1"/>
+    <col min="16" max="16" width="20.5" customWidth="1"/>
+    <col min="17" max="17" width="24.5" customWidth="1"/>
+    <col min="18" max="18" width="27.5" customWidth="1"/>
+    <col min="19" max="19" width="16.25" customWidth="1"/>
+    <col min="20" max="20" width="20.75" customWidth="1"/>
+    <col min="21" max="21" width="15.25" customWidth="1"/>
+    <col min="22" max="22" width="20.875" customWidth="1"/>
+    <col min="23" max="23" width="19.625" customWidth="1"/>
+    <col min="24" max="24" width="21.875" customWidth="1"/>
+    <col min="25" max="25" width="26.375" customWidth="1"/>
+    <col min="26" max="26" width="20.875" customWidth="1"/>
+    <col min="27" max="27" width="27.125" customWidth="1"/>
+    <col min="28" max="28" width="21.875" customWidth="1"/>
+    <col min="29" max="29" width="26.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:29">
+    <row r="1" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2114,7 +1522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="198" customHeight="1" spans="1:29">
+    <row r="2" spans="1:29" ht="198" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -2203,7 +1611,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:29">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -2292,7 +1700,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:29">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>64</v>
       </c>
@@ -2353,7 +1761,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:29">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -2414,7 +1822,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:29">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -2475,7 +1883,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:29">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>85</v>
       </c>
@@ -2502,10 +1910,10 @@
         <v>69</v>
       </c>
       <c r="K7">
-        <v>0.05</v>
+        <v>1.05</v>
       </c>
       <c r="L7">
-        <v>120</v>
+        <v>6</v>
       </c>
       <c r="M7" t="b">
         <v>1</v>
@@ -2546,12 +1954,12 @@
         <v>dmk_laser</v>
       </c>
     </row>
-    <row r="8" spans="1:29">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>92</v>
+      <c r="B8" s="17" t="s">
+        <v>116</v>
       </c>
       <c r="C8" t="str">
         <f>[1]danma!$A$7</f>
@@ -2561,7 +1969,7 @@
         <v>66</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -2576,10 +1984,10 @@
         <v>69</v>
       </c>
       <c r="K8">
-        <v>0.05</v>
+        <v>1.05</v>
       </c>
       <c r="L8">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -2616,15 +2024,15 @@
         <v>1</v>
       </c>
       <c r="Y8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="9" spans="1:29">
-      <c r="A9" t="s">
+      <c r="B9" s="13" t="s">
         <v>95</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>96</v>
       </c>
       <c r="C9" t="str">
         <f>[1]danma!$A$8</f>
@@ -2643,13 +2051,13 @@
         <v>78</v>
       </c>
       <c r="I9" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" t="s">
         <v>97</v>
       </c>
-      <c r="J9" t="s">
-        <v>98</v>
-      </c>
       <c r="K9">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>999999</v>
@@ -2680,12 +2088,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:29">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A10" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>99</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>100</v>
       </c>
       <c r="C10" t="str">
         <f>[1]danma!$A$8</f>
@@ -2704,13 +2112,13 @@
         <v>78</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K10">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>999999</v>
@@ -2741,22 +2149,22 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:29">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A11" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>102</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>103</v>
       </c>
       <c r="C11" t="str">
         <f>[1]danma!$A$6</f>
         <v>dmk_mentos</v>
       </c>
       <c r="D11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="14" t="s">
         <v>104</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>105</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2796,7 +2204,7 @@
         <v>73</v>
       </c>
       <c r="U11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Z11" t="s">
         <v>89</v>
@@ -2812,12 +2220,12 @@
         <v>dmk_ball</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:29">
+    <row r="12" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A12" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="15" t="s">
         <v>107</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>108</v>
       </c>
       <c r="C12" s="1" t="str">
         <f>C11</f>
@@ -2899,12 +2307,12 @@
         <v>dmk_ball</v>
       </c>
     </row>
-    <row r="13" spans="1:29">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>110</v>
       </c>
       <c r="C13" t="str">
         <f>[4]danma!$A$9</f>
@@ -2914,7 +2322,7 @@
         <v>66</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -2957,21 +2365,21 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:29">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" t="s">
         <v>112</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>113</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="D14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3011,12 +2419,12 @@
         <v>73</v>
       </c>
       <c r="U14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>